--- a/artfynd/A 37801-2021 artfynd.xlsx
+++ b/artfynd/A 37801-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37801-2021 artfynd.xlsx
+++ b/artfynd/A 37801-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104973</v>
       </c>
       <c r="B2" t="n">
-        <v>89651</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567177.6840871137</v>
+        <v>567178</v>
       </c>
       <c r="R2" t="n">
-        <v>6615813.609246146</v>
+        <v>6615814</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2010-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +785,7 @@
         <v>66361719</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567183.1220499561</v>
+        <v>567183</v>
       </c>
       <c r="R3" t="n">
-        <v>6615820.779891041</v>
+        <v>6615821</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -921,6 +901,224 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2984048</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sörhagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567168</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6615774</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Betade hagmarker fram till 1962, enligt ortsbefolkningen. Sedan fritt igenvuxet. Spridda förekomster. De flesta mer eller mindre överblommade.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Örtrik blandskog, gläntor.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2593589</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sörhagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567168</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6615774</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog, örtrik</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
